--- a/data/trans_camb/P11_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,82</t>
+          <t>-3,0; 5,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,12</t>
+          <t>-3,75; 4,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 15,77</t>
+          <t>5,64; 15,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,92</t>
+          <t>1,57; 9,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 10,41</t>
+          <t>2,03; 10,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,66; 21,16</t>
+          <t>13,37; 21,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,42</t>
+          <t>0,7; 6,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,08</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,3; 18,29</t>
+          <t>12,06; 18,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 18,38</t>
+          <t>-8,5; 17,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 16,53</t>
+          <t>-10,78; 15,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 50,05</t>
+          <t>16,02; 49,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 19,73</t>
+          <t>3,13; 21,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 22,9</t>
+          <t>4,19; 24,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,69; 47,33</t>
+          <t>27,03; 47,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 16,21</t>
+          <t>1,38; 16,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 17,98</t>
+          <t>2,01; 18,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,18; 46,16</t>
+          <t>28,6; 46,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,77</t>
+          <t>-0,76; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,17</t>
+          <t>1,74; 6,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,53</t>
+          <t>3,6; 14,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,02</t>
+          <t>-0,38; 4,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,81</t>
+          <t>-0,48; 4,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 36,11</t>
+          <t>10,24; 35,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,62</t>
+          <t>0,09; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,01</t>
+          <t>1,27; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 24,23</t>
+          <t>10,07; 25,35</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 36,79</t>
+          <t>-5,89; 36,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,63; 60,8</t>
+          <t>13,48; 57,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,5; 133,15</t>
+          <t>35,66; 134,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 29,58</t>
+          <t>-2,28; 29,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 28,31</t>
+          <t>-2,39; 28,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,11; 206,13</t>
+          <t>54,26; 211,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 25,8</t>
+          <t>0,61; 26,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 36,13</t>
+          <t>8,01; 34,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,29; 161,41</t>
+          <t>65,64; 177,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,64</t>
+          <t>-3,93; 4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,59</t>
+          <t>-4,1; 3,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,79</t>
+          <t>4,4; 12,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; -1,16</t>
+          <t>-10,03; -0,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 3,77</t>
+          <t>-5,59; 4,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 13,17</t>
+          <t>4,17; 13,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,73</t>
+          <t>-5,6; 0,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,4</t>
+          <t>-3,61; 2,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,13</t>
+          <t>5,8; 12,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 55,65</t>
+          <t>-32,1; 53,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 44,6</t>
+          <t>-34,86; 46,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,45; 155,25</t>
+          <t>36,22; 148,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,22; -7,66</t>
+          <t>-53,13; -6,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 27,21</t>
+          <t>-29,34; 27,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,69; 91,41</t>
+          <t>20,55; 93,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 6,22</t>
+          <t>-38,98; 7,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 19,43</t>
+          <t>-23,98; 20,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,57; 104,13</t>
+          <t>38,28; 101,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,69</t>
+          <t>-1,37; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,39</t>
+          <t>-1,26; 2,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,48</t>
+          <t>1,07; 9,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,23</t>
+          <t>-0,21; 4,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,75</t>
+          <t>-2,39; 1,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 22,88</t>
+          <t>6,4; 21,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,95</t>
+          <t>0,04; 3,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,55</t>
+          <t>-1,42; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 15,17</t>
+          <t>5,55; 16,49</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 15,63</t>
+          <t>-7,22; 14,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 13,95</t>
+          <t>-6,66; 14,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 54,17</t>
+          <t>6,24; 53,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 15,03</t>
+          <t>-0,66; 15,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 6,2</t>
+          <t>-7,99; 6,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,23; 78,17</t>
+          <t>21,48; 74,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 12,81</t>
+          <t>0,14; 12,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 6,72</t>
+          <t>-5,77; 6,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,35; 63,7</t>
+          <t>22,93; 70,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P11_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,43</t>
+          <t>16,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>13,96</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,66</t>
+          <t>-2,97; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 4,96</t>
+          <t>-4,34; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 15,69</t>
+          <t>4,73; 14,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,49</t>
+          <t>1,81; 9,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 10,69</t>
+          <t>2,39; 10,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,37; 21,35</t>
+          <t>12,56; 20,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,67</t>
+          <t>0,85; 6,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,78; 7,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,06; 18,33</t>
+          <t>10,87; 17,02</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 17,68</t>
+          <t>-8,59; 17,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 15,45</t>
+          <t>-12,12; 15,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 49,37</t>
+          <t>13,65; 45,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 21,0</t>
+          <t>3,86; 21,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 24,12</t>
+          <t>4,9; 23,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,03; 47,65</t>
+          <t>26,26; 45,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,64</t>
+          <t>1,98; 17,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,25</t>
+          <t>1,63; 18,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,6; 46,83</t>
+          <t>25,88; 43,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>13,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,03</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>12,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,74</t>
+          <t>-0,71; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,03</t>
+          <t>1,66; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 14,54</t>
+          <t>10,64; 15,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,94</t>
+          <t>-0,34; 5,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,96</t>
+          <t>-0,58; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 35,14</t>
+          <t>9,75; 15,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,61</t>
+          <t>0,21; 3,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,8</t>
+          <t>1,3; 4,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 25,35</t>
+          <t>11,16; 14,9</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>115,49%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 36,58</t>
+          <t>-5,6; 34,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 57,83</t>
+          <t>13,02; 58,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,66; 134,44</t>
+          <t>82,13; 152,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 29,29</t>
+          <t>-1,8; 30,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 28,91</t>
+          <t>-2,79; 29,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,26; 211,52</t>
+          <t>49,03; 92,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 26,09</t>
+          <t>0,79; 26,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 34,36</t>
+          <t>8,46; 34,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,64; 177,64</t>
+          <t>71,55; 108,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,07</t>
+          <t>9,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,51</t>
+          <t>-3,63; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,78</t>
+          <t>-4,23; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 12,63</t>
+          <t>4,31; 12,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,91</t>
+          <t>-10,32; -1,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,1</t>
+          <t>-5,37; 3,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,43</t>
+          <t>4,65; 13,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,85</t>
+          <t>-6,05; 0,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,38</t>
+          <t>-3,52; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,07</t>
+          <t>6,24; 12,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 53,07</t>
+          <t>-30,56; 54,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 46,56</t>
+          <t>-34,53; 40,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,22; 148,97</t>
+          <t>32,01; 146,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,13; -6,33</t>
+          <t>-54,62; -8,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 27,68</t>
+          <t>-28,32; 26,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,55; 93,01</t>
+          <t>22,37; 94,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 7,39</t>
+          <t>-39,91; 4,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 20,71</t>
+          <t>-23,39; 22,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,28; 101,73</t>
+          <t>39,56; 104,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>8,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,58</t>
+          <t>-1,32; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,62</t>
+          <t>-1,62; 2,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,43</t>
+          <t>6,06; 10,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 4,22</t>
+          <t>-0,21; 4,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,89</t>
+          <t>-2,44; 1,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,4; 21,81</t>
+          <t>5,88; 9,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,01</t>
+          <t>-0,11; 2,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,55</t>
+          <t>-1,47; 1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 16,49</t>
+          <t>6,81; 9,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 14,77</t>
+          <t>-6,98; 14,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 14,92</t>
+          <t>-8,36; 13,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 53,96</t>
+          <t>31,48; 58,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 15,01</t>
+          <t>-0,7; 15,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 6,76</t>
+          <t>-8,02; 6,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,48; 74,55</t>
+          <t>19,18; 35,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 12,94</t>
+          <t>-0,36; 12,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,68</t>
+          <t>-5,93; 7,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,93; 70,36</t>
+          <t>27,55; 41,95</t>
         </is>
       </c>
     </row>
